--- a/y11603/carbon-clearing/data/audit_report_1_2025-04.xlsx
+++ b/y11603/carbon-clearing/data/audit_report_1_2025-04.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-26 18:01:42.947731</t>
+          <t>2026-05-28 03:18:20.409284</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-26 18:01:43.154685</t>
+          <t>2026-05-28 03:18:20.498318</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
         <v>50000</v>
       </c>
       <c r="D2" t="n">
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="E2" t="n">
         <v>8500</v>
@@ -608,19 +608,19 @@
         <v>-5000</v>
       </c>
       <c r="G2" t="n">
-        <v>66500</v>
+        <v>51500</v>
       </c>
       <c r="H2" t="n">
         <v>56500</v>
       </c>
       <c r="I2" t="n">
-        <v>10000</v>
+        <v>-5000</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>余额差异：计算值66500.0000，申报值56500.0000，差额10000.0000</t>
+          <t>余额差异：计算值51500.0000，申报值56500.0000，差额-5000.0000</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
